--- a/clustering/sepsectors/logistics sector (VDS_s) 0.xlsx
+++ b/clustering/sepsectors/logistics sector (VDS_s) 0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="21">
   <si>
     <t>sector</t>
   </si>
@@ -480,7 +480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="73.7109375" customWidth="1"/>
@@ -798,7 +798,7 @@
         <v>2210689.4932816424</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
         <v>18</v>
       </c>
@@ -819,7 +819,7 @@
         <v>1.0712234055705171E-3</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B18" s="5" t="s">
         <v>19</v>
       </c>
@@ -840,7 +840,7 @@
         <v>1.9714033377901509E-3</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B20" s="5" t="s">
         <v>20</v>
       </c>
@@ -859,6 +859,362 @@
       <c r="G20" s="3">
         <f t="shared" si="2"/>
         <v>0.54338114633168244</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D23" s="3">
+        <v>4855346.2125374135</v>
+      </c>
+      <c r="E23" s="3">
+        <v>135386.12959937999</v>
+      </c>
+      <c r="F23" s="4">
+        <v>3.714330459169155E-3</v>
+      </c>
+      <c r="G23" s="4">
+        <v>1.653323199151599E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D24" s="3">
+        <v>4794949.4413491804</v>
+      </c>
+      <c r="E24" s="3">
+        <v>99309.261365249986</v>
+      </c>
+      <c r="F24" s="4">
+        <v>2.5245281739425698E-3</v>
+      </c>
+      <c r="G24" s="4">
+        <v>8.8733431342220078E-4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D25" s="3">
+        <v>4600808.5022977749</v>
+      </c>
+      <c r="E25" s="3">
+        <v>60802.035819069999</v>
+      </c>
+      <c r="F25" s="4">
+        <v>6.8489439848556958E-3</v>
+      </c>
+      <c r="G25" s="4">
+        <v>8.4462018431121508E-4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D26" s="3">
+        <v>4270265.7526510246</v>
+      </c>
+      <c r="E26" s="3">
+        <v>72255.755925899997</v>
+      </c>
+      <c r="F26" s="4">
+        <v>2.7888505476110981E-2</v>
+      </c>
+      <c r="G26" s="4">
+        <v>1.402683970588293E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="3">
+        <f>AVERAGE(D23:D24)</f>
+        <v>4825147.8269432969</v>
+      </c>
+      <c r="E28" s="3">
+        <f t="shared" ref="E28:G28" si="3">AVERAGE(E23:E24)</f>
+        <v>117347.69548231499</v>
+      </c>
+      <c r="F28" s="4">
+        <f t="shared" si="3"/>
+        <v>3.1194293165558622E-3</v>
+      </c>
+      <c r="G28" s="4">
+        <f t="shared" si="3"/>
+        <v>1.2703287562868999E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="3">
+        <f>AVERAGE(D25:D26)</f>
+        <v>4435537.1274743993</v>
+      </c>
+      <c r="E29" s="3">
+        <f t="shared" ref="E29:G29" si="4">AVERAGE(E25:E26)</f>
+        <v>66528.895872484994</v>
+      </c>
+      <c r="F29" s="4">
+        <f t="shared" si="4"/>
+        <v>1.7368724730483339E-2</v>
+      </c>
+      <c r="G29" s="4">
+        <f t="shared" si="4"/>
+        <v>1.123652077449754E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C31" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="3">
+        <f>D28/D29</f>
+        <v>1.0878384484836321</v>
+      </c>
+      <c r="E31" s="3">
+        <f t="shared" ref="E31:G31" si="5">E28/E29</f>
+        <v>1.7638605592859029</v>
+      </c>
+      <c r="F31" s="3">
+        <f t="shared" si="5"/>
+        <v>0.17960036588529976</v>
+      </c>
+      <c r="G31" s="3">
+        <f t="shared" si="5"/>
+        <v>1.1305356718336195</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D34" s="3">
+        <v>2292248.1387702548</v>
+      </c>
+      <c r="E34" s="3">
+        <v>34254.624294250003</v>
+      </c>
+      <c r="F34" s="4">
+        <v>1.595347631915882E-3</v>
+      </c>
+      <c r="G34" s="4">
+        <v>9.361237617013568E-4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D35" s="3">
+        <v>2266287.1009142809</v>
+      </c>
+      <c r="E35" s="3">
+        <v>31237.990653870002</v>
+      </c>
+      <c r="F35" s="4">
+        <v>4.7806163538082437E-3</v>
+      </c>
+      <c r="G35" s="4">
+        <v>7.032550042484375E-4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D36" s="3">
+        <v>2155091.885649004</v>
+      </c>
+      <c r="E36" s="3">
+        <v>55489.055466000013</v>
+      </c>
+      <c r="F36" s="4">
+        <v>8.0723796852959749E-4</v>
+      </c>
+      <c r="G36" s="4">
+        <v>7.0553447782127363E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D37" s="3">
+        <v>1926632.816358228</v>
+      </c>
+      <c r="E37" s="3">
+        <v>70482.351956779996</v>
+      </c>
+      <c r="F37" s="4">
+        <v>1.720869178633199E-3</v>
+      </c>
+      <c r="G37" s="4">
+        <v>1.9771398616983161E-4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B39" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D39" s="3">
+        <f>AVERAGE(D34:D35)</f>
+        <v>2279267.6198422676</v>
+      </c>
+      <c r="E39" s="3">
+        <f t="shared" ref="E39:G39" si="6">AVERAGE(E34:E35)</f>
+        <v>32746.307474060002</v>
+      </c>
+      <c r="F39" s="4">
+        <f t="shared" si="6"/>
+        <v>3.1879819928620629E-3</v>
+      </c>
+      <c r="G39" s="4">
+        <f t="shared" si="6"/>
+        <v>8.196893829748972E-4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B40" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" s="3">
+        <f>AVERAGE(D36:D37)</f>
+        <v>2040862.3510036161</v>
+      </c>
+      <c r="E40" s="3">
+        <f t="shared" ref="E40:G40" si="7">AVERAGE(E36:E37)</f>
+        <v>62985.703711390001</v>
+      </c>
+      <c r="F40" s="4">
+        <f t="shared" si="7"/>
+        <v>1.2640535735813983E-3</v>
+      </c>
+      <c r="G40" s="4">
+        <f t="shared" si="7"/>
+        <v>3.6265293821912841E-3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C42" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D42" s="3">
+        <f>D39/D40</f>
+        <v>1.116815947298657</v>
+      </c>
+      <c r="E42" s="3">
+        <f t="shared" ref="E42:G42" si="8">E39/E40</f>
+        <v>0.51990063688275234</v>
+      </c>
+      <c r="F42" s="3">
+        <f t="shared" si="8"/>
+        <v>2.5220307584192545</v>
+      </c>
+      <c r="G42" s="3">
+        <f t="shared" si="8"/>
+        <v>0.22602584912178772</v>
       </c>
     </row>
   </sheetData>
@@ -866,6 +1222,198 @@
     <sortCondition descending="1" ref="D2:D13"/>
   </sortState>
   <conditionalFormatting sqref="D2:D13">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E13">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F13">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G13">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D17:D18">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E17:E18">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F17:F18">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G17:G18">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D23:D26">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E23:E26">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F23:F26">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G23:G26">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D28:D29">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E28:E29">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F28:F29">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G28:G29">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D34:D37">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -877,7 +1425,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E13">
+  <conditionalFormatting sqref="E34:E37">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -889,7 +1437,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F13">
+  <conditionalFormatting sqref="F34:F37">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -901,7 +1449,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G13">
+  <conditionalFormatting sqref="G34:G37">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -913,7 +1461,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D17:D18">
+  <conditionalFormatting sqref="D39:D40">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -925,7 +1473,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E17:E18">
+  <conditionalFormatting sqref="E39:E40">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -937,7 +1485,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F17:F18">
+  <conditionalFormatting sqref="F39:F40">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -949,7 +1497,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G17:G18">
+  <conditionalFormatting sqref="G39:G40">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>

--- a/clustering/sepsectors/logistics sector (VDS_s) 0.xlsx
+++ b/clustering/sepsectors/logistics sector (VDS_s) 0.xlsx
@@ -14,12 +14,15 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="22">
   <si>
     <t>sector</t>
   </si>
@@ -82,6 +85,9 @@
   </si>
   <si>
     <t>разница</t>
+  </si>
+  <si>
+    <t>Year</t>
   </si>
 </sst>
 </file>
@@ -159,7 +165,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -177,6 +183,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -193,6 +202,2643 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Деятельность сухопутного и трубопроводного транспорта</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$D$40</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$C$41:$C$44</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.87949768476332302</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.94757578572206147</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.98756076939842574</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$41:$D$44</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.75</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-593A-4573-B9D3-0BF4C66CE8AA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$E$40</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$C$41:$C$44</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.87949768476332302</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.94757578572206147</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.98756076939842574</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$E$41:$E$44</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.53370131888481798</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.44910092340322316</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.73352611274962376</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-593A-4573-B9D3-0BF4C66CE8AA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$F$40</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$C$41:$C$44</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.87949768476332302</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.94757578572206147</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.98756076939842574</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$F$41:$F$44</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.2455830410389841</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.0522175026734791E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.13318499488439112</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-593A-4573-B9D3-0BF4C66CE8AA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$G$40</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$C$41:$C$44</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.87949768476332302</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.94757578572206147</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.98756076939842574</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$G$41:$G$44</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.84840276317908003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.51086211379882107</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.53669743089405353</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-593A-4573-B9D3-0BF4C66CE8AA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="973682783"/>
+        <c:axId val="973684031"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="973682783"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ru-RU" sz="1200">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>ВДС</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ru-RU"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="973684031"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="973684031"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ru-RU" sz="1100">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Значения</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ru-RU"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="973682783"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Складское хозяйство и вспомогательная транспортная деятельность</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$D$40</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$C$65:$C$68</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.84049923905351187</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.94016518072304667</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.98867442079377077</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$D$65:$D$68</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A958-410F-9CDE-BA7A263BF974}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$E$40</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$C$65:$C$68</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.84049923905351187</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.94016518072304667</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.98867442079377077</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$E$65:$E$68</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.78727587722989267</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.44320301162800635</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.48600285522899472</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-A958-410F-9CDE-BA7A263BF974}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$F$40</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$C$65:$C$68</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.84049923905351187</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.94016518072304667</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.98867442079377077</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$F$65:$F$68</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.35996805668422921</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.16885646301371809</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.33371170448451204</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-A958-410F-9CDE-BA7A263BF974}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$G$40</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$C$65:$C$68</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.84049923905351187</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.94016518072304667</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.98867442079377077</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$G$65:$G$68</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2.8023291899267978E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.9676915353608897E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.13268292211489857</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-A958-410F-9CDE-BA7A263BF974}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="973682783"/>
+        <c:axId val="973684031"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="973682783"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ru-RU" sz="1200">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>ВДС</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ru-RU"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="973684031"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="973684031"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ru-RU" sz="1100">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Значения</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ru-RU"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="973682783"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>112059</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>67236</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>517151</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>33900</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Диаграмма 2"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>168087</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>123264</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>573179</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>89928</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Диаграмма 3"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="inf16"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="39">
+          <cell r="D39" t="str">
+            <v>Year</v>
+          </cell>
+          <cell r="E39" t="str">
+            <v>ITcosts_s</v>
+          </cell>
+          <cell r="F39" t="str">
+            <v>skvozcosts_s</v>
+          </cell>
+          <cell r="G39" t="str">
+            <v>trainingcosts_s</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="C40">
+            <v>0.75320035180004941</v>
+          </cell>
+          <cell r="D40">
+            <v>1</v>
+          </cell>
+          <cell r="E40">
+            <v>0.8576536031471178</v>
+          </cell>
+          <cell r="F40">
+            <v>9.4632036706885733E-2</v>
+          </cell>
+          <cell r="G40">
+            <v>0.30845304233506288</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="C41">
+            <v>0.80558451044020529</v>
+          </cell>
+          <cell r="D41">
+            <v>0.75</v>
+          </cell>
+          <cell r="E41">
+            <v>0.80890079918421609</v>
+          </cell>
+          <cell r="F41">
+            <v>0.27164901806536035</v>
+          </cell>
+          <cell r="G41">
+            <v>0.46444703398099701</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="C42">
+            <v>0.94055185443048506</v>
+          </cell>
+          <cell r="D42">
+            <v>0.5</v>
+          </cell>
+          <cell r="E42">
+            <v>0.79155969555065653</v>
+          </cell>
+          <cell r="F42">
+            <v>0.13278607396570202</v>
+          </cell>
+          <cell r="G42">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="C43">
+            <v>1</v>
+          </cell>
+          <cell r="D43">
+            <v>0.25</v>
+          </cell>
+          <cell r="E43">
+            <v>1</v>
+          </cell>
+          <cell r="F43">
+            <v>1</v>
+          </cell>
+          <cell r="G43">
+            <v>0.47223470956791447</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -480,7 +3126,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="73.7109375" customWidth="1"/>
@@ -892,7 +3538,7 @@
         <v>8</v>
       </c>
       <c r="C23" s="2">
-        <v>2023</v>
+        <v>3</v>
       </c>
       <c r="D23" s="3">
         <v>4855346.2125374135</v>
@@ -915,7 +3561,7 @@
         <v>8</v>
       </c>
       <c r="C24" s="2">
-        <v>2024</v>
+        <v>4</v>
       </c>
       <c r="D24" s="3">
         <v>4794949.4413491804</v>
@@ -938,7 +3584,7 @@
         <v>8</v>
       </c>
       <c r="C25" s="2">
-        <v>2022</v>
+        <v>2</v>
       </c>
       <c r="D25" s="3">
         <v>4600808.5022977749</v>
@@ -961,7 +3607,7 @@
         <v>8</v>
       </c>
       <c r="C26" s="2">
-        <v>2021</v>
+        <v>1</v>
       </c>
       <c r="D26" s="3">
         <v>4270265.7526510246</v>
@@ -1040,186 +3686,610 @@
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
+      <c r="C33" s="2">
+        <f>MAX(C23:C26)</f>
+        <v>4</v>
+      </c>
+      <c r="D33" s="2">
+        <f t="shared" ref="D33:G33" si="6">MAX(D23:D26)</f>
+        <v>4855346.2125374135</v>
+      </c>
+      <c r="E33" s="2">
+        <f t="shared" si="6"/>
+        <v>135386.12959937999</v>
+      </c>
+      <c r="F33" s="2">
+        <f t="shared" si="6"/>
+        <v>2.7888505476110981E-2</v>
+      </c>
+      <c r="G33" s="2">
+        <f t="shared" si="6"/>
+        <v>1.653323199151599E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C34" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C35" s="2">
+        <f>C23/C$33</f>
+        <v>0.75</v>
+      </c>
+      <c r="D35" s="2">
+        <f>D23/D$33</f>
+        <v>1</v>
+      </c>
+      <c r="E35" s="2">
+        <f>E23/E$33</f>
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <f>F23/F$33</f>
+        <v>0.13318499488439112</v>
+      </c>
+      <c r="G35" s="2">
+        <f>G23/G$33</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C36" s="2">
+        <f t="shared" ref="C36:C38" si="7">C24/C$33</f>
+        <v>1</v>
+      </c>
+      <c r="D36" s="2">
+        <f t="shared" ref="D36:G38" si="8">D24/D$33</f>
+        <v>0.98756076939842574</v>
+      </c>
+      <c r="E36" s="2">
+        <f t="shared" si="8"/>
+        <v>0.73352611274962376</v>
+      </c>
+      <c r="F36" s="2">
+        <f t="shared" si="8"/>
+        <v>9.0522175026734791E-2</v>
+      </c>
+      <c r="G36" s="2">
+        <f t="shared" si="8"/>
+        <v>0.53669743089405353</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C37" s="2">
+        <f t="shared" si="7"/>
+        <v>0.5</v>
+      </c>
+      <c r="D37" s="2">
+        <f t="shared" si="8"/>
+        <v>0.94757578572206147</v>
+      </c>
+      <c r="E37" s="2">
+        <f t="shared" si="8"/>
+        <v>0.44910092340322316</v>
+      </c>
+      <c r="F37" s="2">
+        <f t="shared" si="8"/>
+        <v>0.2455830410389841</v>
+      </c>
+      <c r="G37" s="2">
+        <f t="shared" si="8"/>
+        <v>0.51086211379882107</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C38" s="2">
+        <f t="shared" si="7"/>
+        <v>0.25</v>
+      </c>
+      <c r="D38" s="2">
+        <f t="shared" si="8"/>
+        <v>0.87949768476332302</v>
+      </c>
+      <c r="E38" s="2">
+        <f t="shared" si="8"/>
+        <v>0.53370131888481798</v>
+      </c>
+      <c r="F38" s="2">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="G38" s="2">
+        <f t="shared" si="8"/>
+        <v>0.84840276317908003</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C40" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C41" s="2">
+        <v>0.87949768476332302</v>
+      </c>
+      <c r="D41" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E41" s="2">
+        <v>0.53370131888481798</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1</v>
+      </c>
+      <c r="G41" s="2">
+        <v>0.84840276317908003</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C42" s="2">
+        <v>0.94757578572206147</v>
+      </c>
+      <c r="D42" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E42" s="2">
+        <v>0.44910092340322316</v>
+      </c>
+      <c r="F42" s="2">
+        <v>0.2455830410389841</v>
+      </c>
+      <c r="G42" s="2">
+        <v>0.51086211379882107</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C43" s="2">
+        <v>0.98756076939842574</v>
+      </c>
+      <c r="D43" s="2">
+        <v>1</v>
+      </c>
+      <c r="E43" s="2">
+        <v>0.73352611274962376</v>
+      </c>
+      <c r="F43" s="2">
+        <v>9.0522175026734791E-2</v>
+      </c>
+      <c r="G43" s="2">
+        <v>0.53669743089405353</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C44" s="2">
+        <v>1</v>
+      </c>
+      <c r="D44" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E44" s="2">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2">
+        <v>0.13318499488439112</v>
+      </c>
+      <c r="G44" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B46" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C46" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D46" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E46" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F46" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="G46" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B47" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C34" s="2">
-        <v>2024</v>
-      </c>
-      <c r="D34" s="3">
+      <c r="C47" s="2">
+        <v>4</v>
+      </c>
+      <c r="D47" s="3">
         <v>2292248.1387702548</v>
       </c>
-      <c r="E34" s="3">
+      <c r="E47" s="3">
         <v>34254.624294250003</v>
       </c>
-      <c r="F34" s="4">
+      <c r="F47" s="4">
         <v>1.595347631915882E-3</v>
       </c>
-      <c r="G34" s="4">
+      <c r="G47" s="4">
         <v>9.361237617013568E-4</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B48" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C35" s="2">
-        <v>2023</v>
-      </c>
-      <c r="D35" s="3">
+      <c r="C48" s="2">
+        <v>3</v>
+      </c>
+      <c r="D48" s="3">
         <v>2266287.1009142809</v>
       </c>
-      <c r="E35" s="3">
+      <c r="E48" s="3">
         <v>31237.990653870002</v>
       </c>
-      <c r="F35" s="4">
+      <c r="F48" s="4">
         <v>4.7806163538082437E-3</v>
       </c>
-      <c r="G35" s="4">
+      <c r="G48" s="4">
         <v>7.032550042484375E-4</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B49" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C36" s="2">
-        <v>2022</v>
-      </c>
-      <c r="D36" s="3">
+      <c r="C49" s="2">
+        <v>2</v>
+      </c>
+      <c r="D49" s="3">
         <v>2155091.885649004</v>
       </c>
-      <c r="E36" s="3">
+      <c r="E49" s="3">
         <v>55489.055466000013</v>
       </c>
-      <c r="F36" s="4">
+      <c r="F49" s="4">
         <v>8.0723796852959749E-4</v>
       </c>
-      <c r="G36" s="4">
+      <c r="G49" s="4">
         <v>7.0553447782127363E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B50" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C37" s="2">
-        <v>2021</v>
-      </c>
-      <c r="D37" s="3">
+      <c r="C50" s="2">
+        <v>1</v>
+      </c>
+      <c r="D50" s="3">
         <v>1926632.816358228</v>
       </c>
-      <c r="E37" s="3">
+      <c r="E50" s="3">
         <v>70482.351956779996</v>
       </c>
-      <c r="F37" s="4">
+      <c r="F50" s="4">
         <v>1.720869178633199E-3</v>
       </c>
-      <c r="G37" s="4">
+      <c r="G50" s="4">
         <v>1.9771398616983161E-4</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B39" s="5" t="s">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B52" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D39" s="3">
-        <f>AVERAGE(D34:D35)</f>
+      <c r="D52" s="3">
+        <f>AVERAGE(D47:D48)</f>
         <v>2279267.6198422676</v>
       </c>
-      <c r="E39" s="3">
-        <f t="shared" ref="E39:G39" si="6">AVERAGE(E34:E35)</f>
+      <c r="E52" s="3">
+        <f t="shared" ref="E52:G52" si="9">AVERAGE(E47:E48)</f>
         <v>32746.307474060002</v>
       </c>
-      <c r="F39" s="4">
-        <f t="shared" si="6"/>
+      <c r="F52" s="4">
+        <f t="shared" si="9"/>
         <v>3.1879819928620629E-3</v>
       </c>
-      <c r="G39" s="4">
-        <f t="shared" si="6"/>
+      <c r="G52" s="4">
+        <f t="shared" si="9"/>
         <v>8.196893829748972E-4</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B40" s="5" t="s">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B53" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D40" s="3">
-        <f>AVERAGE(D36:D37)</f>
+      <c r="D53" s="3">
+        <f>AVERAGE(D49:D50)</f>
         <v>2040862.3510036161</v>
       </c>
-      <c r="E40" s="3">
-        <f t="shared" ref="E40:G40" si="7">AVERAGE(E36:E37)</f>
+      <c r="E53" s="3">
+        <f t="shared" ref="E53:G53" si="10">AVERAGE(E49:E50)</f>
         <v>62985.703711390001</v>
       </c>
-      <c r="F40" s="4">
-        <f t="shared" si="7"/>
+      <c r="F53" s="4">
+        <f t="shared" si="10"/>
         <v>1.2640535735813983E-3</v>
       </c>
-      <c r="G40" s="4">
-        <f t="shared" si="7"/>
+      <c r="G53" s="4">
+        <f t="shared" si="10"/>
         <v>3.6265293821912841E-3</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C42" s="5" t="s">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C55" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D42" s="3">
-        <f>D39/D40</f>
+      <c r="D55" s="3">
+        <f>D52/D53</f>
         <v>1.116815947298657</v>
       </c>
-      <c r="E42" s="3">
-        <f t="shared" ref="E42:G42" si="8">E39/E40</f>
+      <c r="E55" s="3">
+        <f t="shared" ref="E55:G55" si="11">E52/E53</f>
         <v>0.51990063688275234</v>
       </c>
-      <c r="F42" s="3">
-        <f t="shared" si="8"/>
+      <c r="F55" s="3">
+        <f t="shared" si="11"/>
         <v>2.5220307584192545</v>
       </c>
-      <c r="G42" s="3">
-        <f t="shared" si="8"/>
+      <c r="G55" s="3">
+        <f t="shared" si="11"/>
         <v>0.22602584912178772</v>
       </c>
     </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C57" s="2">
+        <f>MAX(C47:C50)</f>
+        <v>4</v>
+      </c>
+      <c r="D57" s="2">
+        <f t="shared" ref="D57:G57" si="12">MAX(D47:D50)</f>
+        <v>2292248.1387702548</v>
+      </c>
+      <c r="E57" s="2">
+        <f t="shared" si="12"/>
+        <v>70482.351956779996</v>
+      </c>
+      <c r="F57" s="2">
+        <f t="shared" si="12"/>
+        <v>4.7806163538082437E-3</v>
+      </c>
+      <c r="G57" s="2">
+        <f t="shared" si="12"/>
+        <v>7.0553447782127363E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C58" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C59" s="2">
+        <f>C47/C$57</f>
+        <v>1</v>
+      </c>
+      <c r="D59" s="2">
+        <f>D47/D$57</f>
+        <v>1</v>
+      </c>
+      <c r="E59" s="2">
+        <f>E47/E$57</f>
+        <v>0.48600285522899472</v>
+      </c>
+      <c r="F59" s="2">
+        <f>F47/F$57</f>
+        <v>0.33371170448451204</v>
+      </c>
+      <c r="G59" s="2">
+        <f>G47/G$57</f>
+        <v>0.13268292211489857</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C60" s="2">
+        <f t="shared" ref="C60:C62" si="13">C48/C$57</f>
+        <v>0.75</v>
+      </c>
+      <c r="D60" s="2">
+        <f t="shared" ref="D60:G62" si="14">D48/D$57</f>
+        <v>0.98867442079377077</v>
+      </c>
+      <c r="E60" s="2">
+        <f t="shared" si="14"/>
+        <v>0.44320301162800635</v>
+      </c>
+      <c r="F60" s="2">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="G60" s="2">
+        <f t="shared" si="14"/>
+        <v>9.9676915353608897E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C61" s="2">
+        <f t="shared" si="13"/>
+        <v>0.5</v>
+      </c>
+      <c r="D61" s="2">
+        <f t="shared" si="14"/>
+        <v>0.94016518072304667</v>
+      </c>
+      <c r="E61" s="2">
+        <f t="shared" si="14"/>
+        <v>0.78727587722989267</v>
+      </c>
+      <c r="F61" s="2">
+        <f t="shared" si="14"/>
+        <v>0.16885646301371809</v>
+      </c>
+      <c r="G61" s="2">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C62" s="2">
+        <f t="shared" si="13"/>
+        <v>0.25</v>
+      </c>
+      <c r="D62" s="2">
+        <f t="shared" si="14"/>
+        <v>0.84049923905351187</v>
+      </c>
+      <c r="E62" s="2">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="F62" s="2">
+        <f t="shared" si="14"/>
+        <v>0.35996805668422921</v>
+      </c>
+      <c r="G62" s="2">
+        <f t="shared" si="14"/>
+        <v>2.8023291899267978E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C64" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C65" s="2">
+        <v>0.84049923905351187</v>
+      </c>
+      <c r="D65" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E65" s="2">
+        <v>1</v>
+      </c>
+      <c r="F65" s="2">
+        <v>0.35996805668422921</v>
+      </c>
+      <c r="G65" s="2">
+        <v>2.8023291899267978E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C66" s="2">
+        <v>0.94016518072304667</v>
+      </c>
+      <c r="D66" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E66" s="2">
+        <v>0.78727587722989267</v>
+      </c>
+      <c r="F66" s="2">
+        <v>0.16885646301371809</v>
+      </c>
+      <c r="G66" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C67" s="2">
+        <v>0.98867442079377077</v>
+      </c>
+      <c r="D67" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E67" s="2">
+        <v>0.44320301162800635</v>
+      </c>
+      <c r="F67" s="2">
+        <v>1</v>
+      </c>
+      <c r="G67" s="2">
+        <v>9.9676915353608897E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C68" s="2">
+        <v>1</v>
+      </c>
+      <c r="D68" s="2">
+        <v>1</v>
+      </c>
+      <c r="E68" s="2">
+        <v>0.48600285522899472</v>
+      </c>
+      <c r="F68" s="2">
+        <v>0.33371170448451204</v>
+      </c>
+      <c r="G68" s="2">
+        <v>0.13268292211489857</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState ref="A2:G13">
-    <sortCondition descending="1" ref="D2:D13"/>
+  <sortState ref="C65:G68">
+    <sortCondition ref="C65:C68"/>
   </sortState>
   <conditionalFormatting sqref="D2:D13">
     <cfRule type="colorScale" priority="24">
@@ -1413,7 +4483,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D34:D37">
+  <conditionalFormatting sqref="D47:D50">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -1425,7 +4495,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E34:E37">
+  <conditionalFormatting sqref="E47:E50">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -1437,7 +4507,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F34:F37">
+  <conditionalFormatting sqref="F47:F50">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -1449,7 +4519,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G34:G37">
+  <conditionalFormatting sqref="G47:G50">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -1461,7 +4531,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D39:D40">
+  <conditionalFormatting sqref="D52:D53">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -1473,7 +4543,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E39:E40">
+  <conditionalFormatting sqref="E52:E53">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -1485,7 +4555,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F39:F40">
+  <conditionalFormatting sqref="F52:F53">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -1497,7 +4567,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G39:G40">
+  <conditionalFormatting sqref="G52:G53">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -1510,5 +4580,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/clustering/sepsectors/logistics sector (VDS_s) 0.xlsx
+++ b/clustering/sepsectors/logistics sector (VDS_s) 0.xlsx
@@ -238,8 +238,10 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="ru-RU"/>
-              <a:t>Деятельность сухопутного и трубопроводного транспорта</a:t>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>49</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -277,19 +279,19 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$D$40</c:f>
+              <c:f>Sheet1!$C$41</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Year</c:v>
+                  <c:v>0,88</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -297,7 +299,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="tx1"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -307,29 +309,28 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:cat>
-            <c:numRef>
-              <c:f>Sheet1!$C$41:$C$44</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
+            <c:strRef>
+              <c:f>Sheet1!$D$40:$G$40</c:f>
+              <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.87949768476332302</c:v>
+                  <c:v>Year</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.94757578572206147</c:v>
+                  <c:v>ITcosts_s</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.98756076939842574</c:v>
+                  <c:v>skvozcosts_s</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1</c:v>
+                  <c:v>trainingcosts_s</c:v>
                 </c:pt>
-              </c:numCache>
-            </c:numRef>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$41:$D$44</c:f>
+              <c:f>Sheet1!$D$41:$G$41</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -337,184 +338,33 @@
                   <c:v>0.25</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.5</c:v>
+                  <c:v>0.53370131888481798</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.75</c:v>
+                  <c:v>0.84840276317908003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-593A-4573-B9D3-0BF4C66CE8AA}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$E$40</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>Sheet1!$C$41:$C$44</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.87949768476332302</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.94757578572206147</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.98756076939842574</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$E$41:$E$44</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.53370131888481798</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.44910092340322316</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.73352611274962376</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-593A-4573-B9D3-0BF4C66CE8AA}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$F$40</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>Sheet1!$C$41:$C$44</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.87949768476332302</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.94757578572206147</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.98756076939842574</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$F$41:$F$44</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.2455830410389841</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>9.0522175026734791E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.13318499488439112</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-593A-4573-B9D3-0BF4C66CE8AA}"/>
+              <c16:uniqueId val="{00000000-EECE-4548-8440-409DB84FEE50}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
-          <c:order val="3"/>
+          <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$G$40</c:f>
+              <c:f>Sheet1!$C$44</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>trainingcosts_s</c:v>
+                  <c:v>1,00</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -532,40 +382,39 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$D$40:$G$40</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$41:$C$44</c:f>
+              <c:f>Sheet1!$D$44:$G$44</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.87949768476332302</c:v>
+                  <c:v>0.75</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.94757578572206147</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.98756076939842574</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$G$41:$G$44</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.84840276317908003</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.51086211379882107</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.53669743089405353</c:v>
+                  <c:v>0.13318499488439112</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>1</c:v>
@@ -573,10 +422,9 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-593A-4573-B9D3-0BF4C66CE8AA}"/>
+              <c16:uniqueId val="{00000003-EECE-4548-8440-409DB84FEE50}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -588,71 +436,16 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:smooth val="0"/>
-        <c:axId val="973682783"/>
-        <c:axId val="973684031"/>
-      </c:lineChart>
+        <c:axId val="744722240"/>
+        <c:axId val="744723072"/>
+      </c:radarChart>
       <c:catAx>
-        <c:axId val="973682783"/>
+        <c:axId val="744722240"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="ru-RU" sz="1200">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>ВДС</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:layout/>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:sysClr val="windowText" lastClr="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="ru-RU"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -675,12 +468,9 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -690,7 +480,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="973684031"/>
+        <c:crossAx val="744723072"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -698,7 +488,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="973684031"/>
+        <c:axId val="744723072"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -718,60 +508,6 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="ru-RU" sz="1100">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>Значения</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:layout/>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:sysClr val="windowText" lastClr="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="ru-RU"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -788,12 +524,9 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -803,7 +536,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="973682783"/>
+        <c:crossAx val="744722240"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -816,7 +549,7 @@
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="b"/>
+      <c:legendPos val="t"/>
       <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
@@ -831,12 +564,9 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -918,8 +648,10 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="ru-RU"/>
-              <a:t>Складское хозяйство и вспомогательная транспортная деятельность</a:t>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>52</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -957,19 +689,19 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$D$40</c:f>
+              <c:f>Sheet1!$C$65</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Year</c:v>
+                  <c:v>0,84</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -977,7 +709,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="tx1"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -987,29 +719,28 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:cat>
-            <c:numRef>
-              <c:f>Sheet1!$C$65:$C$68</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
+            <c:strRef>
+              <c:f>Sheet1!$D$40:$G$40</c:f>
+              <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.84049923905351187</c:v>
+                  <c:v>Year</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.94016518072304667</c:v>
+                  <c:v>ITcosts_s</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.98867442079377077</c:v>
+                  <c:v>skvozcosts_s</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1</c:v>
+                  <c:v>trainingcosts_s</c:v>
                 </c:pt>
-              </c:numCache>
-            </c:numRef>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$65:$D$68</c:f>
+              <c:f>Sheet1!$D$65:$G$65</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -1017,184 +748,33 @@
                   <c:v>0.25</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.5</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.75</c:v>
+                  <c:v>0.35996805668422921</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1</c:v>
+                  <c:v>2.8023291899267978E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A958-410F-9CDE-BA7A263BF974}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$E$40</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>ITcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>Sheet1!$C$65:$C$68</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.84049923905351187</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.94016518072304667</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.98867442079377077</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$E$65:$E$68</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.78727587722989267</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.44320301162800635</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.48600285522899472</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-A958-410F-9CDE-BA7A263BF974}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$F$40</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>skvozcosts_s</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>Sheet1!$C$65:$C$68</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.84049923905351187</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.94016518072304667</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.98867442079377077</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$F$65:$F$68</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.35996805668422921</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.16885646301371809</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.33371170448451204</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-A958-410F-9CDE-BA7A263BF974}"/>
+              <c16:uniqueId val="{00000000-38C0-4A83-8830-DCD67A12197E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
-          <c:order val="3"/>
+          <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$G$40</c:f>
+              <c:f>Sheet1!$C$68</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>trainingcosts_s</c:v>
+                  <c:v>1,00</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1212,40 +792,39 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$D$40:$G$40</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
             <c:numRef>
-              <c:f>Sheet1!$C$65:$C$68</c:f>
+              <c:f>Sheet1!$D$68:$G$68</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0.84049923905351187</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.94016518072304667</c:v>
+                  <c:v>0.48600285522899472</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.98867442079377077</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$G$65:$G$68</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>2.8023291899267978E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>9.9676915353608897E-2</c:v>
+                  <c:v>0.33371170448451204</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0.13268292211489857</c:v>
@@ -1253,10 +832,9 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-A958-410F-9CDE-BA7A263BF974}"/>
+              <c16:uniqueId val="{00000003-38C0-4A83-8830-DCD67A12197E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1268,71 +846,16 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:smooth val="0"/>
-        <c:axId val="973682783"/>
-        <c:axId val="973684031"/>
-      </c:lineChart>
+        <c:axId val="744722240"/>
+        <c:axId val="744723072"/>
+      </c:radarChart>
       <c:catAx>
-        <c:axId val="973682783"/>
+        <c:axId val="744722240"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="ru-RU" sz="1200">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>ВДС</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:layout/>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:sysClr val="windowText" lastClr="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="ru-RU"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -1355,12 +878,9 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -1370,7 +890,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="973684031"/>
+        <c:crossAx val="744723072"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1378,7 +898,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="973684031"/>
+        <c:axId val="744723072"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1398,60 +918,6 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="ru-RU" sz="1100">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000"/>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>Значения</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:layout/>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:sysClr val="windowText" lastClr="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="ru-RU"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -1468,12 +934,9 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -1483,7 +946,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="973682783"/>
+        <c:crossAx val="744722240"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1496,7 +959,7 @@
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="b"/>
+      <c:legendPos val="t"/>
       <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
@@ -1511,12 +974,9 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -1645,7 +1105,7 @@
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -1753,11 +1213,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -1768,11 +1223,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
@@ -1804,9 +1254,6 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1862,22 +1309,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -1982,8 +1430,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -2115,19 +1563,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -2161,7 +1610,7 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -2269,11 +1718,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -2284,11 +1728,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
@@ -2320,9 +1759,6 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2378,22 +1814,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -2498,8 +1935,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -2631,19 +2068,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -2680,20 +2118,20 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>112059</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>67236</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>212911</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>22412</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>517151</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>33900</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>330536</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>158191</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Диаграмма 2"/>
+        <xdr:cNvPr id="5" name="Диаграмма 4"/>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -2712,20 +2150,20 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>168087</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>123264</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>435429</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>176893</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>573179</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>89928</xdr:rowOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>553053</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>122172</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Диаграмма 3"/>
+        <xdr:cNvPr id="6" name="Диаграмма 5"/>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -2749,93 +2187,97 @@
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
-      <sheetName val="inf16"/>
+      <sheetName val="Original"/>
+      <sheetName val="Only best"/>
+      <sheetName val="Best|Worst"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
-        <row r="39">
-          <cell r="D39" t="str">
+        <row r="89">
+          <cell r="D89" t="str">
             <v>Year</v>
           </cell>
-          <cell r="E39" t="str">
+          <cell r="E89" t="str">
             <v>ITcosts_s</v>
           </cell>
-          <cell r="F39" t="str">
+          <cell r="F89" t="str">
             <v>skvozcosts_s</v>
           </cell>
-          <cell r="G39" t="str">
+          <cell r="G89" t="str">
             <v>trainingcosts_s</v>
           </cell>
         </row>
-        <row r="40">
-          <cell r="C40">
-            <v>0.75320035180004941</v>
+        <row r="90">
+          <cell r="C90">
+            <v>0.60541707637600206</v>
           </cell>
-          <cell r="D40">
+          <cell r="D90">
+            <v>0.75</v>
+          </cell>
+          <cell r="E90">
             <v>1</v>
           </cell>
-          <cell r="E40">
-            <v>0.8576536031471178</v>
+          <cell r="F90">
+            <v>0.80661939562538798</v>
           </cell>
-          <cell r="F40">
-            <v>9.4632036706885733E-2</v>
-          </cell>
-          <cell r="G40">
-            <v>0.30845304233506288</v>
+          <cell r="G90">
+            <v>0.45477225885659545</v>
           </cell>
         </row>
-        <row r="41">
-          <cell r="C41">
-            <v>0.80558451044020529</v>
+        <row r="91">
+          <cell r="C91">
+            <v>0.62826451624711255</v>
           </cell>
-          <cell r="D41">
-            <v>0.75</v>
+          <cell r="D91">
+            <v>1</v>
           </cell>
-          <cell r="E41">
-            <v>0.80890079918421609</v>
+          <cell r="E91">
+            <v>0.7323973572762863</v>
           </cell>
-          <cell r="F41">
-            <v>0.27164901806536035</v>
+          <cell r="F91">
+            <v>0.9611546957323327</v>
           </cell>
-          <cell r="G41">
-            <v>0.46444703398099701</v>
+          <cell r="G91">
+            <v>0.83771179639168136</v>
           </cell>
         </row>
-        <row r="42">
-          <cell r="C42">
-            <v>0.94055185443048506</v>
+        <row r="92">
+          <cell r="C92">
+            <v>0.78924387345553881</v>
           </cell>
-          <cell r="D42">
+          <cell r="D92">
             <v>0.5</v>
           </cell>
-          <cell r="E42">
-            <v>0.79155969555065653</v>
+          <cell r="E92">
+            <v>0.90624842311195075</v>
           </cell>
-          <cell r="F42">
-            <v>0.13278607396570202</v>
+          <cell r="F92">
+            <v>1</v>
           </cell>
-          <cell r="G42">
+          <cell r="G92">
+            <v>0.67809276193519175</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="C93">
+            <v>1</v>
+          </cell>
+          <cell r="D93">
+            <v>0.25</v>
+          </cell>
+          <cell r="E93">
+            <v>0.89882061387652312</v>
+          </cell>
+          <cell r="F93">
+            <v>0.17795127025264079</v>
+          </cell>
+          <cell r="G93">
             <v>1</v>
           </cell>
         </row>
-        <row r="43">
-          <cell r="C43">
-            <v>1</v>
-          </cell>
-          <cell r="D43">
-            <v>0.25</v>
-          </cell>
-          <cell r="E43">
-            <v>1</v>
-          </cell>
-          <cell r="F43">
-            <v>1</v>
-          </cell>
-          <cell r="G43">
-            <v>0.47223470956791447</v>
-          </cell>
-        </row>
       </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3830,7 +3272,7 @@
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C41" s="2">
+      <c r="C41" s="3">
         <v>0.87949768476332302</v>
       </c>
       <c r="D41" s="2">
@@ -3847,7 +3289,7 @@
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C42" s="2">
+      <c r="C42" s="3">
         <v>0.94757578572206147</v>
       </c>
       <c r="D42" s="2">
@@ -3864,7 +3306,7 @@
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C43" s="2">
+      <c r="C43" s="3">
         <v>0.98756076939842574</v>
       </c>
       <c r="D43" s="2">
@@ -3881,7 +3323,7 @@
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C44" s="2">
+      <c r="C44" s="3">
         <v>1</v>
       </c>
       <c r="D44" s="2">
@@ -4220,7 +3662,7 @@
       </c>
     </row>
     <row r="65" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C65" s="2">
+      <c r="C65" s="3">
         <v>0.84049923905351187</v>
       </c>
       <c r="D65" s="2">
@@ -4237,7 +3679,7 @@
       </c>
     </row>
     <row r="66" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C66" s="2">
+      <c r="C66" s="3">
         <v>0.94016518072304667</v>
       </c>
       <c r="D66" s="2">
@@ -4254,7 +3696,7 @@
       </c>
     </row>
     <row r="67" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C67" s="2">
+      <c r="C67" s="3">
         <v>0.98867442079377077</v>
       </c>
       <c r="D67" s="2">
@@ -4271,7 +3713,7 @@
       </c>
     </row>
     <row r="68" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C68" s="2">
+      <c r="C68" s="3">
         <v>1</v>
       </c>
       <c r="D68" s="2">

--- a/clustering/sepsectors/logistics sector (VDS_s) 0.xlsx
+++ b/clustering/sepsectors/logistics sector (VDS_s) 0.xlsx
@@ -14,15 +14,12 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="24">
   <si>
     <t>sector</t>
   </si>
@@ -88,6 +85,12 @@
   </si>
   <si>
     <t>Year</t>
+  </si>
+  <si>
+    <t>best</t>
+  </si>
+  <si>
+    <t>worst</t>
   </si>
 </sst>
 </file>
@@ -2183,106 +2186,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Original"/>
-      <sheetName val="Only best"/>
-      <sheetName val="Best|Worst"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="89">
-          <cell r="D89" t="str">
-            <v>Year</v>
-          </cell>
-          <cell r="E89" t="str">
-            <v>ITcosts_s</v>
-          </cell>
-          <cell r="F89" t="str">
-            <v>skvozcosts_s</v>
-          </cell>
-          <cell r="G89" t="str">
-            <v>trainingcosts_s</v>
-          </cell>
-        </row>
-        <row r="90">
-          <cell r="C90">
-            <v>0.60541707637600206</v>
-          </cell>
-          <cell r="D90">
-            <v>0.75</v>
-          </cell>
-          <cell r="E90">
-            <v>1</v>
-          </cell>
-          <cell r="F90">
-            <v>0.80661939562538798</v>
-          </cell>
-          <cell r="G90">
-            <v>0.45477225885659545</v>
-          </cell>
-        </row>
-        <row r="91">
-          <cell r="C91">
-            <v>0.62826451624711255</v>
-          </cell>
-          <cell r="D91">
-            <v>1</v>
-          </cell>
-          <cell r="E91">
-            <v>0.7323973572762863</v>
-          </cell>
-          <cell r="F91">
-            <v>0.9611546957323327</v>
-          </cell>
-          <cell r="G91">
-            <v>0.83771179639168136</v>
-          </cell>
-        </row>
-        <row r="92">
-          <cell r="C92">
-            <v>0.78924387345553881</v>
-          </cell>
-          <cell r="D92">
-            <v>0.5</v>
-          </cell>
-          <cell r="E92">
-            <v>0.90624842311195075</v>
-          </cell>
-          <cell r="F92">
-            <v>1</v>
-          </cell>
-          <cell r="G92">
-            <v>0.67809276193519175</v>
-          </cell>
-        </row>
-        <row r="93">
-          <cell r="C93">
-            <v>1</v>
-          </cell>
-          <cell r="D93">
-            <v>0.25</v>
-          </cell>
-          <cell r="E93">
-            <v>0.89882061387652312</v>
-          </cell>
-          <cell r="F93">
-            <v>0.17795127025264079</v>
-          </cell>
-          <cell r="G93">
-            <v>1</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2568,7 +2471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:L84"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="73.7109375" customWidth="1"/>
@@ -3127,7 +3030,7 @@
         <v>1.1305356718336195</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C33" s="2">
         <f>MAX(C23:C26)</f>
         <v>4</v>
@@ -3149,7 +3052,7 @@
         <v>1.653323199151599E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C34" s="7" t="s">
         <v>21</v>
       </c>
@@ -3165,8 +3068,15 @@
       <c r="G34" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J34" s="2"/>
+      <c r="K34" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L34" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C35" s="2">
         <f>C23/C$33</f>
         <v>0.75</v>
@@ -3187,8 +3097,17 @@
         <f>G23/G$33</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J35" s="7">
+        <v>49</v>
+      </c>
+      <c r="K35" s="3">
+        <v>0.88318499488439106</v>
+      </c>
+      <c r="L35" s="3">
+        <v>0.86381505128993619</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C36" s="2">
         <f t="shared" ref="C36:C38" si="7">C24/C$33</f>
         <v>1</v>
@@ -3209,8 +3128,17 @@
         <f t="shared" si="8"/>
         <v>0.53669743089405353</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J36" s="7">
+        <v>52</v>
+      </c>
+      <c r="K36" s="3">
+        <v>0.4125742313208246</v>
+      </c>
+      <c r="L36" s="3">
+        <v>0.31353068479296026</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C37" s="2">
         <f t="shared" si="7"/>
         <v>0.5</v>
@@ -3232,7 +3160,7 @@
         <v>0.51086211379882107</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C38" s="2">
         <f t="shared" si="7"/>
         <v>0.25</v>
@@ -3254,7 +3182,7 @@
         <v>0.84840276317908003</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C40" s="7" t="s">
         <v>3</v>
       </c>
@@ -3271,7 +3199,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C41" s="3">
         <v>0.87949768476332302</v>
       </c>
@@ -3288,7 +3216,7 @@
         <v>0.84840276317908003</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C42" s="3">
         <v>0.94757578572206147</v>
       </c>
@@ -3305,7 +3233,7 @@
         <v>0.51086211379882107</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C43" s="3">
         <v>0.98756076939842574</v>
       </c>
@@ -3322,7 +3250,7 @@
         <v>0.53669743089405353</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C44" s="3">
         <v>1</v>
       </c>
@@ -3339,7 +3267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>0</v>
       </c>
@@ -3362,7 +3290,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>13</v>
       </c>
@@ -3385,7 +3313,7 @@
         <v>9.361237617013568E-4</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>13</v>
       </c>
@@ -3408,7 +3336,7 @@
         <v>7.032550042484375E-4</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>13</v>
       </c>
@@ -3431,7 +3359,7 @@
         <v>7.0553447782127363E-3</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>13</v>
       </c>
@@ -3454,7 +3382,7 @@
         <v>1.9771398616983161E-4</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B52" s="5" t="s">
         <v>18</v>
       </c>
@@ -3475,7 +3403,7 @@
         <v>8.196893829748972E-4</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B53" s="5" t="s">
         <v>19</v>
       </c>
@@ -3496,7 +3424,7 @@
         <v>3.6265293821912841E-3</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C55" s="5" t="s">
         <v>20</v>
       </c>
@@ -3517,7 +3445,7 @@
         <v>0.22602584912178772</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C57" s="2">
         <f>MAX(C47:C50)</f>
         <v>4</v>
@@ -3539,7 +3467,7 @@
         <v>7.0553447782127363E-3</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C58" s="7" t="s">
         <v>21</v>
       </c>
@@ -3555,8 +3483,15 @@
       <c r="G58" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J58" s="2"/>
+      <c r="K58" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L58" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C59" s="2">
         <f>C47/C$57</f>
         <v>1</v>
@@ -3577,8 +3512,19 @@
         <f>G47/G$57</f>
         <v>0.13268292211489857</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J59" s="7">
+        <v>49</v>
+      </c>
+      <c r="K59" s="3">
+        <f>0.5*(D44*E44+E44*F44+F44*G44+G44*D44)</f>
+        <v>0.88318499488439106</v>
+      </c>
+      <c r="L59" s="3">
+        <f>0.5*(D41*E41+E41*F41+F41*G41+G41*D41)</f>
+        <v>0.86381505128993619</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C60" s="2">
         <f t="shared" ref="C60:C62" si="13">C48/C$57</f>
         <v>0.75</v>
@@ -3600,7 +3546,7 @@
         <v>9.9676915353608897E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C61" s="2">
         <f t="shared" si="13"/>
         <v>0.5</v>
@@ -3622,7 +3568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C62" s="2">
         <f t="shared" si="13"/>
         <v>0.25</v>
@@ -3644,7 +3590,7 @@
         <v>2.8023291899267978E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C64" s="7" t="s">
         <v>3</v>
       </c>
@@ -3661,7 +3607,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C65" s="3">
         <v>0.84049923905351187</v>
       </c>
@@ -3678,7 +3624,7 @@
         <v>2.8023291899267978E-2</v>
       </c>
     </row>
-    <row r="66" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C66" s="3">
         <v>0.94016518072304667</v>
       </c>
@@ -3695,7 +3641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C67" s="3">
         <v>0.98867442079377077</v>
       </c>
@@ -3712,7 +3658,7 @@
         <v>9.9676915353608897E-2</v>
       </c>
     </row>
-    <row r="68" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C68" s="3">
         <v>1</v>
       </c>
@@ -3728,6 +3674,43 @@
       <c r="G68" s="2">
         <v>0.13268292211489857</v>
       </c>
+    </row>
+    <row r="77" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="J77" s="2"/>
+      <c r="K77" s="7"/>
+      <c r="L77" s="7"/>
+    </row>
+    <row r="78" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="J78" s="7"/>
+      <c r="K78" s="3"/>
+      <c r="L78" s="3"/>
+    </row>
+    <row r="82" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J82" s="2"/>
+      <c r="K82" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L82" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="83" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J83" s="7">
+        <v>52</v>
+      </c>
+      <c r="K83" s="3">
+        <f>0.5*(D68*E68+E68*F68+F68*G68+G68*D68)</f>
+        <v>0.4125742313208246</v>
+      </c>
+      <c r="L83" s="3">
+        <f>0.5*(D65*E65+E65*F65+F65*G65+G65*D65)</f>
+        <v>0.31353068479296026</v>
+      </c>
+    </row>
+    <row r="84" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J84" s="7"/>
+      <c r="K84" s="3"/>
+      <c r="L84" s="3"/>
     </row>
   </sheetData>
   <sortState ref="C65:G68">

--- a/clustering/sepsectors/logistics sector (VDS_s) 0.xlsx
+++ b/clustering/sepsectors/logistics sector (VDS_s) 0.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12885"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12885"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3181,6 +3181,14 @@
         <f t="shared" si="8"/>
         <v>0.84840276317908003</v>
       </c>
+      <c r="K38" s="3">
+        <f>AVERAGE(K35:K36)</f>
+        <v>0.64787961310260789</v>
+      </c>
+      <c r="L38" s="3">
+        <f>AVERAGE(L35:L36)</f>
+        <v>0.58867286804144825</v>
+      </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C40" s="7" t="s">

--- a/clustering/sepsectors/logistics sector (VDS_s) 0.xlsx
+++ b/clustering/sepsectors/logistics sector (VDS_s) 0.xlsx
@@ -9,17 +9,21 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12885"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12885"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1 (2)" sheetId="2" r:id="rId2"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId3"/>
+  </externalReferences>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="24">
   <si>
     <t>sector</t>
   </si>
@@ -1027,6 +1031,800 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>49</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$C$41</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,88</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$E$40:$G$40</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sheet1 (2)'!$E$41:$G$41</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.53370131888481798</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.84840276317908003</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E5D7-4893-99D7-D5ED34C5BB64}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$C$44</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1,00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$E$40:$G$40</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sheet1 (2)'!$E$44:$G$44</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.13318499488439112</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-E5D7-4893-99D7-D5ED34C5BB64}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="285497360"/>
+        <c:axId val="285495696"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="285497360"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="285495696"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="285495696"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="285497360"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>52</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$C$65</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,84</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$E$40:$G$40</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sheet1 (2)'!$E$65:$G$65</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.35996805668422921</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.8023291899267978E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D133-47D0-B929-3178E5EEBB4D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$C$68</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1,00</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Sheet1 (2)'!$E$40:$G$40</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sheet1 (2)'!$E$68:$G$68</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.48600285522899472</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.33371170448451204</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.13268292211489857</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-D133-47D0-B929-3178E5EEBB4D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="285497360"/>
+        <c:axId val="285495696"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="285497360"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="285495696"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="285495696"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="285497360"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1107,6 +1905,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
   <cs:axisTitle>
@@ -1613,6 +2491,1016 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -2184,6 +4072,158 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>598714</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>81643</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>432955</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>128403</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Диаграмма 3"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>54430</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>81643</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>500992</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>128403</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Диаграмма 4"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Sheet1 (2)"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="42">
+          <cell r="E42" t="str">
+            <v>ITcosts_s</v>
+          </cell>
+          <cell r="F42" t="str">
+            <v>skvozcosts_s</v>
+          </cell>
+          <cell r="G42" t="str">
+            <v>trainingcosts_s</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="C43">
+            <v>0.53195397442833625</v>
+          </cell>
+          <cell r="E43">
+            <v>1</v>
+          </cell>
+          <cell r="F43">
+            <v>0.4341128768543896</v>
+          </cell>
+          <cell r="G43">
+            <v>0.96268324181002174</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="C44">
+            <v>0.74071957251902487</v>
+          </cell>
+          <cell r="E44">
+            <v>0.81436789578742097</v>
+          </cell>
+          <cell r="F44">
+            <v>1</v>
+          </cell>
+          <cell r="G44">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="C45">
+            <v>0.88899585107146872</v>
+          </cell>
+          <cell r="E45">
+            <v>0.3732928962109599</v>
+          </cell>
+          <cell r="F45">
+            <v>0.78623653793827153</v>
+          </cell>
+          <cell r="G45">
+            <v>0.50683853134311552</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="C46">
+            <v>1</v>
+          </cell>
+          <cell r="E46">
+            <v>0.37449706271284755</v>
+          </cell>
+          <cell r="F46">
+            <v>0.59247665944601891</v>
+          </cell>
+          <cell r="G46">
+            <v>0.50683853134311552</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4016,4 +6056,1550 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L84"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="73.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" customWidth="1"/>
+    <col min="6" max="6" width="17.140625" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D2" s="3">
+        <v>4855346.2125374135</v>
+      </c>
+      <c r="E2" s="3">
+        <v>135386.12959937999</v>
+      </c>
+      <c r="F2" s="4">
+        <v>3.714330459169155E-3</v>
+      </c>
+      <c r="G2" s="4">
+        <v>1.653323199151599E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D3" s="3">
+        <v>4794949.4413491804</v>
+      </c>
+      <c r="E3" s="3">
+        <v>99309.261365249986</v>
+      </c>
+      <c r="F3" s="4">
+        <v>2.5245281739425698E-3</v>
+      </c>
+      <c r="G3" s="4">
+        <v>8.8733431342220078E-4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D4" s="3">
+        <v>4600808.5022977749</v>
+      </c>
+      <c r="E4" s="3">
+        <v>60802.035819069999</v>
+      </c>
+      <c r="F4" s="4">
+        <v>6.8489439848556958E-3</v>
+      </c>
+      <c r="G4" s="4">
+        <v>8.4462018431121508E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D5" s="3">
+        <v>4270265.7526510246</v>
+      </c>
+      <c r="E5" s="3">
+        <v>72255.755925899997</v>
+      </c>
+      <c r="F5" s="4">
+        <v>2.7888505476110981E-2</v>
+      </c>
+      <c r="G5" s="4">
+        <v>1.402683970588293E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2024</v>
+      </c>
+      <c r="D6" s="3">
+        <v>2292248.1387702548</v>
+      </c>
+      <c r="E6" s="3">
+        <v>34254.624294250003</v>
+      </c>
+      <c r="F6" s="4">
+        <v>1.595347631915882E-3</v>
+      </c>
+      <c r="G6" s="4">
+        <v>9.361237617013568E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D7" s="3">
+        <v>2266287.1009142809</v>
+      </c>
+      <c r="E7" s="3">
+        <v>31237.990653870002</v>
+      </c>
+      <c r="F7" s="4">
+        <v>4.7806163538082437E-3</v>
+      </c>
+      <c r="G7" s="4">
+        <v>7.032550042484375E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D8" s="3">
+        <v>2155091.885649004</v>
+      </c>
+      <c r="E8" s="3">
+        <v>55489.055466000013</v>
+      </c>
+      <c r="F8" s="4">
+        <v>8.0723796852959749E-4</v>
+      </c>
+      <c r="G8" s="4">
+        <v>7.0553447782127363E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1926632.816358228</v>
+      </c>
+      <c r="E9" s="3">
+        <v>70482.351956779996</v>
+      </c>
+      <c r="F9" s="4">
+        <v>1.720869178633199E-3</v>
+      </c>
+      <c r="G9" s="4">
+        <v>1.9771398616983161E-4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="2">
+        <v>2023</v>
+      </c>
+      <c r="D10" s="3">
+        <v>297348.59581775579</v>
+      </c>
+      <c r="E10" s="3">
+        <v>16286.65164027</v>
+      </c>
+      <c r="F10" s="4">
+        <v>1.754538540588953E-4</v>
+      </c>
+      <c r="G10" s="4">
+        <v>1.917541117093744E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D11" s="3">
+        <v>234330.45241976029</v>
+      </c>
+      <c r="E11" s="3">
+        <v>5602.2332923599997</v>
+      </c>
+      <c r="F11" s="4">
+        <v>1.6046617180793979E-4</v>
+      </c>
+      <c r="G11" s="4">
+        <v>1.7497075699021261E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="2">
+        <v>2022</v>
+      </c>
+      <c r="D12" s="3">
+        <v>160888.6352920986</v>
+      </c>
+      <c r="E12" s="3">
+        <v>893.32115457000009</v>
+      </c>
+      <c r="F12" s="4">
+        <v>6.8539092001545414E-3</v>
+      </c>
+      <c r="G12" s="4">
+        <v>6.0481966338306683E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="2">
+        <v>2021</v>
+      </c>
+      <c r="D13" s="3">
+        <v>133123.48380322519</v>
+      </c>
+      <c r="E13" s="3">
+        <v>1151.69215446</v>
+      </c>
+      <c r="F13" s="4">
+        <v>3.5158370961540082E-5</v>
+      </c>
+      <c r="G13" s="4">
+        <v>1.878029724891315E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="3">
+        <f>MEDIAN(D2:D13)</f>
+        <v>2210689.4932816424</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="3">
+        <f>AVERAGE(D2:D7)</f>
+        <v>3846650.8580866549</v>
+      </c>
+      <c r="E17" s="3">
+        <f t="shared" ref="E17:G17" si="0">AVERAGE(E2:E7)</f>
+        <v>72207.632942953322</v>
+      </c>
+      <c r="F17" s="4">
+        <f t="shared" si="0"/>
+        <v>7.892045346633755E-3</v>
+      </c>
+      <c r="G17" s="4">
+        <f t="shared" si="0"/>
+        <v>1.0712234055705171E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="3">
+        <f>AVERAGE(D8:D13)</f>
+        <v>817902.6448900121</v>
+      </c>
+      <c r="E18" s="3">
+        <f t="shared" ref="E18:G18" si="1">AVERAGE(E8:E13)</f>
+        <v>24984.217610740001</v>
+      </c>
+      <c r="F18" s="4">
+        <f t="shared" si="1"/>
+        <v>1.6255157906909521E-3</v>
+      </c>
+      <c r="G18" s="4">
+        <f t="shared" si="1"/>
+        <v>1.9714033377901509E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="3">
+        <f>D17/D18</f>
+        <v>4.7030669018119333</v>
+      </c>
+      <c r="E20" s="3">
+        <f t="shared" ref="E20:G20" si="2">E17/E18</f>
+        <v>2.8901298438864593</v>
+      </c>
+      <c r="F20" s="3">
+        <f t="shared" si="2"/>
+        <v>4.8551022339063907</v>
+      </c>
+      <c r="G20" s="3">
+        <f t="shared" si="2"/>
+        <v>0.54338114633168244</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="2">
+        <v>3</v>
+      </c>
+      <c r="D23" s="3">
+        <v>4855346.2125374135</v>
+      </c>
+      <c r="E23" s="3">
+        <v>135386.12959937999</v>
+      </c>
+      <c r="F23" s="4">
+        <v>3.714330459169155E-3</v>
+      </c>
+      <c r="G23" s="4">
+        <v>1.653323199151599E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="2">
+        <v>4</v>
+      </c>
+      <c r="D24" s="3">
+        <v>4794949.4413491804</v>
+      </c>
+      <c r="E24" s="3">
+        <v>99309.261365249986</v>
+      </c>
+      <c r="F24" s="4">
+        <v>2.5245281739425698E-3</v>
+      </c>
+      <c r="G24" s="4">
+        <v>8.8733431342220078E-4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2">
+        <v>2</v>
+      </c>
+      <c r="D25" s="3">
+        <v>4600808.5022977749</v>
+      </c>
+      <c r="E25" s="3">
+        <v>60802.035819069999</v>
+      </c>
+      <c r="F25" s="4">
+        <v>6.8489439848556958E-3</v>
+      </c>
+      <c r="G25" s="4">
+        <v>8.4462018431121508E-4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="2">
+        <v>1</v>
+      </c>
+      <c r="D26" s="3">
+        <v>4270265.7526510246</v>
+      </c>
+      <c r="E26" s="3">
+        <v>72255.755925899997</v>
+      </c>
+      <c r="F26" s="4">
+        <v>2.7888505476110981E-2</v>
+      </c>
+      <c r="G26" s="4">
+        <v>1.402683970588293E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="3">
+        <f>AVERAGE(D23:D24)</f>
+        <v>4825147.8269432969</v>
+      </c>
+      <c r="E28" s="3">
+        <f t="shared" ref="E28:G28" si="3">AVERAGE(E23:E24)</f>
+        <v>117347.69548231499</v>
+      </c>
+      <c r="F28" s="4">
+        <f t="shared" si="3"/>
+        <v>3.1194293165558622E-3</v>
+      </c>
+      <c r="G28" s="4">
+        <f t="shared" si="3"/>
+        <v>1.2703287562868999E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="3">
+        <f>AVERAGE(D25:D26)</f>
+        <v>4435537.1274743993</v>
+      </c>
+      <c r="E29" s="3">
+        <f t="shared" ref="E29:G29" si="4">AVERAGE(E25:E26)</f>
+        <v>66528.895872484994</v>
+      </c>
+      <c r="F29" s="4">
+        <f t="shared" si="4"/>
+        <v>1.7368724730483339E-2</v>
+      </c>
+      <c r="G29" s="4">
+        <f t="shared" si="4"/>
+        <v>1.123652077449754E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C31" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="3">
+        <f>D28/D29</f>
+        <v>1.0878384484836321</v>
+      </c>
+      <c r="E31" s="3">
+        <f t="shared" ref="E31:G31" si="5">E28/E29</f>
+        <v>1.7638605592859029</v>
+      </c>
+      <c r="F31" s="3">
+        <f t="shared" si="5"/>
+        <v>0.17960036588529976</v>
+      </c>
+      <c r="G31" s="3">
+        <f t="shared" si="5"/>
+        <v>1.1305356718336195</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C33" s="2">
+        <f>MAX(C23:C26)</f>
+        <v>4</v>
+      </c>
+      <c r="D33" s="2">
+        <f t="shared" ref="D33:G33" si="6">MAX(D23:D26)</f>
+        <v>4855346.2125374135</v>
+      </c>
+      <c r="E33" s="2">
+        <f t="shared" si="6"/>
+        <v>135386.12959937999</v>
+      </c>
+      <c r="F33" s="2">
+        <f t="shared" si="6"/>
+        <v>2.7888505476110981E-2</v>
+      </c>
+      <c r="G33" s="2">
+        <f t="shared" si="6"/>
+        <v>1.653323199151599E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C34" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J34" s="2"/>
+      <c r="K34" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L34" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C35" s="2">
+        <f>C23/C$33</f>
+        <v>0.75</v>
+      </c>
+      <c r="D35" s="2">
+        <f>D23/D$33</f>
+        <v>1</v>
+      </c>
+      <c r="E35" s="2">
+        <f>E23/E$33</f>
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <f>F23/F$33</f>
+        <v>0.13318499488439112</v>
+      </c>
+      <c r="G35" s="2">
+        <f>G23/G$33</f>
+        <v>1</v>
+      </c>
+      <c r="J35" s="7">
+        <v>49</v>
+      </c>
+      <c r="K35" s="3">
+        <v>0.88318499488439106</v>
+      </c>
+      <c r="L35" s="3">
+        <v>0.86381505128993619</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C36" s="2">
+        <f t="shared" ref="C36:G38" si="7">C24/C$33</f>
+        <v>1</v>
+      </c>
+      <c r="D36" s="2">
+        <f t="shared" si="7"/>
+        <v>0.98756076939842574</v>
+      </c>
+      <c r="E36" s="2">
+        <f t="shared" si="7"/>
+        <v>0.73352611274962376</v>
+      </c>
+      <c r="F36" s="2">
+        <f t="shared" si="7"/>
+        <v>9.0522175026734791E-2</v>
+      </c>
+      <c r="G36" s="2">
+        <f t="shared" si="7"/>
+        <v>0.53669743089405353</v>
+      </c>
+      <c r="J36" s="7">
+        <v>52</v>
+      </c>
+      <c r="K36" s="3">
+        <v>0.4125742313208246</v>
+      </c>
+      <c r="L36" s="3">
+        <v>0.31353068479296026</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C37" s="2">
+        <f t="shared" si="7"/>
+        <v>0.5</v>
+      </c>
+      <c r="D37" s="2">
+        <f t="shared" si="7"/>
+        <v>0.94757578572206147</v>
+      </c>
+      <c r="E37" s="2">
+        <f t="shared" si="7"/>
+        <v>0.44910092340322316</v>
+      </c>
+      <c r="F37" s="2">
+        <f t="shared" si="7"/>
+        <v>0.2455830410389841</v>
+      </c>
+      <c r="G37" s="2">
+        <f t="shared" si="7"/>
+        <v>0.51086211379882107</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C38" s="2">
+        <f t="shared" si="7"/>
+        <v>0.25</v>
+      </c>
+      <c r="D38" s="2">
+        <f t="shared" si="7"/>
+        <v>0.87949768476332302</v>
+      </c>
+      <c r="E38" s="2">
+        <f t="shared" si="7"/>
+        <v>0.53370131888481798</v>
+      </c>
+      <c r="F38" s="2">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="G38" s="2">
+        <f t="shared" si="7"/>
+        <v>0.84840276317908003</v>
+      </c>
+      <c r="K38" s="3">
+        <f>AVERAGE(K35:K36)</f>
+        <v>0.64787961310260789</v>
+      </c>
+      <c r="L38" s="3">
+        <f>AVERAGE(L35:L36)</f>
+        <v>0.58867286804144825</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C40" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C41" s="3">
+        <v>0.87949768476332302</v>
+      </c>
+      <c r="D41" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E41" s="2">
+        <v>0.53370131888481798</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1</v>
+      </c>
+      <c r="G41" s="2">
+        <v>0.84840276317908003</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C42" s="3">
+        <v>0.94757578572206147</v>
+      </c>
+      <c r="D42" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E42" s="2">
+        <v>0.44910092340322316</v>
+      </c>
+      <c r="F42" s="2">
+        <v>0.2455830410389841</v>
+      </c>
+      <c r="G42" s="2">
+        <v>0.51086211379882107</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C43" s="3">
+        <v>0.98756076939842574</v>
+      </c>
+      <c r="D43" s="2">
+        <v>1</v>
+      </c>
+      <c r="E43" s="2">
+        <v>0.73352611274962376</v>
+      </c>
+      <c r="F43" s="2">
+        <v>9.0522175026734791E-2</v>
+      </c>
+      <c r="G43" s="2">
+        <v>0.53669743089405353</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C44" s="3">
+        <v>1</v>
+      </c>
+      <c r="D44" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E44" s="2">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2">
+        <v>0.13318499488439112</v>
+      </c>
+      <c r="G44" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C47" s="2">
+        <v>4</v>
+      </c>
+      <c r="D47" s="3">
+        <v>2292248.1387702548</v>
+      </c>
+      <c r="E47" s="3">
+        <v>34254.624294250003</v>
+      </c>
+      <c r="F47" s="4">
+        <v>1.595347631915882E-3</v>
+      </c>
+      <c r="G47" s="4">
+        <v>9.361237617013568E-4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C48" s="2">
+        <v>3</v>
+      </c>
+      <c r="D48" s="3">
+        <v>2266287.1009142809</v>
+      </c>
+      <c r="E48" s="3">
+        <v>31237.990653870002</v>
+      </c>
+      <c r="F48" s="4">
+        <v>4.7806163538082437E-3</v>
+      </c>
+      <c r="G48" s="4">
+        <v>7.032550042484375E-4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C49" s="2">
+        <v>2</v>
+      </c>
+      <c r="D49" s="3">
+        <v>2155091.885649004</v>
+      </c>
+      <c r="E49" s="3">
+        <v>55489.055466000013</v>
+      </c>
+      <c r="F49" s="4">
+        <v>8.0723796852959749E-4</v>
+      </c>
+      <c r="G49" s="4">
+        <v>7.0553447782127363E-3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C50" s="2">
+        <v>1</v>
+      </c>
+      <c r="D50" s="3">
+        <v>1926632.816358228</v>
+      </c>
+      <c r="E50" s="3">
+        <v>70482.351956779996</v>
+      </c>
+      <c r="F50" s="4">
+        <v>1.720869178633199E-3</v>
+      </c>
+      <c r="G50" s="4">
+        <v>1.9771398616983161E-4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B52" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D52" s="3">
+        <f>AVERAGE(D47:D48)</f>
+        <v>2279267.6198422676</v>
+      </c>
+      <c r="E52" s="3">
+        <f t="shared" ref="E52:G52" si="8">AVERAGE(E47:E48)</f>
+        <v>32746.307474060002</v>
+      </c>
+      <c r="F52" s="4">
+        <f t="shared" si="8"/>
+        <v>3.1879819928620629E-3</v>
+      </c>
+      <c r="G52" s="4">
+        <f t="shared" si="8"/>
+        <v>8.196893829748972E-4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B53" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D53" s="3">
+        <f>AVERAGE(D49:D50)</f>
+        <v>2040862.3510036161</v>
+      </c>
+      <c r="E53" s="3">
+        <f t="shared" ref="E53:G53" si="9">AVERAGE(E49:E50)</f>
+        <v>62985.703711390001</v>
+      </c>
+      <c r="F53" s="4">
+        <f t="shared" si="9"/>
+        <v>1.2640535735813983E-3</v>
+      </c>
+      <c r="G53" s="4">
+        <f t="shared" si="9"/>
+        <v>3.6265293821912841E-3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C55" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D55" s="3">
+        <f>D52/D53</f>
+        <v>1.116815947298657</v>
+      </c>
+      <c r="E55" s="3">
+        <f t="shared" ref="E55:G55" si="10">E52/E53</f>
+        <v>0.51990063688275234</v>
+      </c>
+      <c r="F55" s="3">
+        <f t="shared" si="10"/>
+        <v>2.5220307584192545</v>
+      </c>
+      <c r="G55" s="3">
+        <f t="shared" si="10"/>
+        <v>0.22602584912178772</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C57" s="2">
+        <f>MAX(C47:C50)</f>
+        <v>4</v>
+      </c>
+      <c r="D57" s="2">
+        <f t="shared" ref="D57:G57" si="11">MAX(D47:D50)</f>
+        <v>2292248.1387702548</v>
+      </c>
+      <c r="E57" s="2">
+        <f t="shared" si="11"/>
+        <v>70482.351956779996</v>
+      </c>
+      <c r="F57" s="2">
+        <f t="shared" si="11"/>
+        <v>4.7806163538082437E-3</v>
+      </c>
+      <c r="G57" s="2">
+        <f t="shared" si="11"/>
+        <v>7.0553447782127363E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C58" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J58" s="2"/>
+      <c r="K58" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L58" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C59" s="2">
+        <f>C47/C$57</f>
+        <v>1</v>
+      </c>
+      <c r="D59" s="2">
+        <f>D47/D$57</f>
+        <v>1</v>
+      </c>
+      <c r="E59" s="2">
+        <f>E47/E$57</f>
+        <v>0.48600285522899472</v>
+      </c>
+      <c r="F59" s="2">
+        <f>F47/F$57</f>
+        <v>0.33371170448451204</v>
+      </c>
+      <c r="G59" s="2">
+        <f>G47/G$57</f>
+        <v>0.13268292211489857</v>
+      </c>
+      <c r="J59" s="7">
+        <v>49</v>
+      </c>
+      <c r="K59" s="3">
+        <f>0.5*(D44*E44+E44*F44+F44*G44+G44*D44)</f>
+        <v>0.88318499488439106</v>
+      </c>
+      <c r="L59" s="3">
+        <f>0.5*(D41*E41+E41*F41+F41*G41+G41*D41)</f>
+        <v>0.86381505128993619</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C60" s="2">
+        <f t="shared" ref="C60:G62" si="12">C48/C$57</f>
+        <v>0.75</v>
+      </c>
+      <c r="D60" s="2">
+        <f t="shared" si="12"/>
+        <v>0.98867442079377077</v>
+      </c>
+      <c r="E60" s="2">
+        <f t="shared" si="12"/>
+        <v>0.44320301162800635</v>
+      </c>
+      <c r="F60" s="2">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="G60" s="2">
+        <f t="shared" si="12"/>
+        <v>9.9676915353608897E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C61" s="2">
+        <f t="shared" si="12"/>
+        <v>0.5</v>
+      </c>
+      <c r="D61" s="2">
+        <f t="shared" si="12"/>
+        <v>0.94016518072304667</v>
+      </c>
+      <c r="E61" s="2">
+        <f t="shared" si="12"/>
+        <v>0.78727587722989267</v>
+      </c>
+      <c r="F61" s="2">
+        <f t="shared" si="12"/>
+        <v>0.16885646301371809</v>
+      </c>
+      <c r="G61" s="2">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C62" s="2">
+        <f t="shared" si="12"/>
+        <v>0.25</v>
+      </c>
+      <c r="D62" s="2">
+        <f t="shared" si="12"/>
+        <v>0.84049923905351187</v>
+      </c>
+      <c r="E62" s="2">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="F62" s="2">
+        <f t="shared" si="12"/>
+        <v>0.35996805668422921</v>
+      </c>
+      <c r="G62" s="2">
+        <f t="shared" si="12"/>
+        <v>2.8023291899267978E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="C64" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C65" s="3">
+        <v>0.84049923905351187</v>
+      </c>
+      <c r="D65" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E65" s="2">
+        <v>1</v>
+      </c>
+      <c r="F65" s="2">
+        <v>0.35996805668422921</v>
+      </c>
+      <c r="G65" s="2">
+        <v>2.8023291899267978E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C66" s="3">
+        <v>0.94016518072304667</v>
+      </c>
+      <c r="D66" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E66" s="2">
+        <v>0.78727587722989267</v>
+      </c>
+      <c r="F66" s="2">
+        <v>0.16885646301371809</v>
+      </c>
+      <c r="G66" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C67" s="3">
+        <v>0.98867442079377077</v>
+      </c>
+      <c r="D67" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E67" s="2">
+        <v>0.44320301162800635</v>
+      </c>
+      <c r="F67" s="2">
+        <v>1</v>
+      </c>
+      <c r="G67" s="2">
+        <v>9.9676915353608897E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C68" s="3">
+        <v>1</v>
+      </c>
+      <c r="D68" s="2">
+        <v>1</v>
+      </c>
+      <c r="E68" s="2">
+        <v>0.48600285522899472</v>
+      </c>
+      <c r="F68" s="2">
+        <v>0.33371170448451204</v>
+      </c>
+      <c r="G68" s="2">
+        <v>0.13268292211489857</v>
+      </c>
+    </row>
+    <row r="77" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="J77" s="2"/>
+      <c r="K77" s="7"/>
+      <c r="L77" s="7"/>
+    </row>
+    <row r="78" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="J78" s="7"/>
+      <c r="K78" s="3"/>
+      <c r="L78" s="3"/>
+    </row>
+    <row r="82" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J82" s="2"/>
+      <c r="K82" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L82" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="83" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J83" s="7">
+        <v>52</v>
+      </c>
+      <c r="K83" s="3">
+        <f>0.5*(D68*E68+E68*F68+F68*G68+G68*D68)</f>
+        <v>0.4125742313208246</v>
+      </c>
+      <c r="L83" s="3">
+        <f>0.5*(D65*E65+E65*F65+F65*G65+G65*D65)</f>
+        <v>0.31353068479296026</v>
+      </c>
+    </row>
+    <row r="84" spans="10:12" x14ac:dyDescent="0.25">
+      <c r="J84" s="7"/>
+      <c r="K84" s="3"/>
+      <c r="L84" s="3"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D2:D13">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E13">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F13">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G13">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D17:D18">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E17:E18">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F17:F18">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G17:G18">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D23:D26">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E23:E26">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F23:F26">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G23:G26">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D28:D29">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E28:E29">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F28:F29">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G28:G29">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D47:D50">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E47:E50">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F47:F50">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G47:G50">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D52:D53">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E52:E53">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F52:F53">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G52:G53">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>